--- a/source/Hoyeh Menu Jun 26.xlsx
+++ b/source/Hoyeh Menu Jun 26.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/chef_hoyeh_jrgroup_com_sg/Documents/Desktop/RWS Mob/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/om_hoyeh_jrgroup_com_sg/Documents/Desktop/menu-rws hoyeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B9EBA44-D3D0-4669-8BA1-A8183BB88044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{6B9EBA44-D3D0-4669-8BA1-A8183BB88044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C1C835E-AE1B-4DDD-B632-EEB3552D8CB7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1610,9 +1608,6 @@
     <t>BBQ Chicken Chop with Raisin Rice</t>
   </si>
   <si>
-    <t>Soya Chicken Rice</t>
-  </si>
-  <si>
     <t>Garlic Spinach</t>
   </si>
   <si>
@@ -1729,6 +1724,9 @@
   </si>
   <si>
     <t>Tumeric Dory Fish</t>
+  </si>
+  <si>
+    <t>Fish Burger W/fries</t>
   </si>
 </sst>
 </file>
@@ -2557,30 +2555,57 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2592,33 +2617,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3002,8 +3000,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="99"/>
-      <c r="B3" s="100"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="3">
         <v>46174</v>
       </c>
@@ -3204,7 +3202,7 @@
         <v>299</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>267</v>
@@ -3221,7 +3219,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -3248,7 +3246,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="102"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="19" t="s">
         <v>270</v>
       </c>
@@ -3262,7 +3260,7 @@
         <v>47</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>271</v>
@@ -3273,7 +3271,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="102"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="65" t="s">
         <v>444</v>
       </c>
@@ -3298,7 +3296,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="102"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="19" t="s">
         <v>81</v>
       </c>
@@ -3323,7 +3321,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="102"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
@@ -3340,7 +3338,7 @@
         <v>296</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>282</v>
@@ -3348,7 +3346,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="103"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
@@ -3453,7 +3451,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -3482,7 +3480,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="95"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -3496,7 +3494,7 @@
         <v>485</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>494</v>
@@ -3505,12 +3503,12 @@
         <v>293</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="95"/>
-      <c r="B22" s="101" t="s">
+      <c r="A22" s="94"/>
+      <c r="B22" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -3536,8 +3534,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="95"/>
-      <c r="B23" s="102"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="31" t="s">
         <v>450</v>
       </c>
@@ -3561,8 +3559,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="95"/>
-      <c r="B24" s="102"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="31" t="s">
         <v>77</v>
       </c>
@@ -3586,8 +3584,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="95"/>
-      <c r="B25" s="102"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="19" t="s">
         <v>301</v>
       </c>
@@ -3611,8 +3609,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="95"/>
-      <c r="B26" s="102"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="92"/>
       <c r="C26" s="19" t="s">
         <v>113</v>
       </c>
@@ -3632,12 +3630,12 @@
         <v>306</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="95"/>
-      <c r="B27" s="103"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="93"/>
       <c r="C27" s="20" t="s">
         <v>83</v>
       </c>
@@ -3651,7 +3649,7 @@
         <v>308</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H27" s="17" t="s">
         <v>84</v>
@@ -3661,7 +3659,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="95"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="17" t="s">
         <v>58</v>
       </c>
@@ -3688,7 +3686,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="95"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -3715,7 +3713,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="96"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="38" t="s">
         <v>59</v>
       </c>
@@ -3742,7 +3740,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="97" t="s">
+      <c r="A31" s="96" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -3771,7 +3769,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="98"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -3782,7 +3780,7 @@
         <v>299</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>267</v>
@@ -3798,8 +3796,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="98"/>
-      <c r="B33" s="101" t="s">
+      <c r="A33" s="97"/>
+      <c r="B33" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -3825,8 +3823,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="98"/>
-      <c r="B34" s="102"/>
+      <c r="A34" s="97"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="19" t="s">
         <v>270</v>
       </c>
@@ -3850,8 +3848,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="98"/>
-      <c r="B35" s="102"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="92"/>
       <c r="C35" s="19" t="s">
         <v>81</v>
       </c>
@@ -3875,8 +3873,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="98"/>
-      <c r="B36" s="102"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="92"/>
       <c r="C36" s="19" t="s">
         <v>51</v>
       </c>
@@ -3893,15 +3891,15 @@
         <v>296</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="98"/>
-      <c r="B37" s="102"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="19" t="s">
         <v>28</v>
       </c>
@@ -3925,7 +3923,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="98"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="17" t="s">
         <v>58</v>
       </c>
@@ -3952,7 +3950,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="98"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -4459,8 +4457,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="83"/>
-      <c r="B3" s="84"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="66">
         <v>46181</v>
       </c>
@@ -4608,7 +4606,7 @@
         <v>457</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G8" s="30" t="s">
         <v>95</v>
@@ -4637,7 +4635,7 @@
         <v>320</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>316</v>
@@ -4658,7 +4656,7 @@
         <v>211</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>456</v>
@@ -4673,12 +4671,12 @@
         <v>99</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -4705,7 +4703,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="92"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="19" t="s">
         <v>100</v>
       </c>
@@ -4719,7 +4717,7 @@
         <v>101</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>102</v>
@@ -4730,7 +4728,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="92"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="19" t="s">
         <v>317</v>
       </c>
@@ -4755,7 +4753,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="92"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="19" t="s">
         <v>103</v>
       </c>
@@ -4780,7 +4778,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="92"/>
+      <c r="B15" s="101"/>
       <c r="C15" s="19" t="s">
         <v>107</v>
       </c>
@@ -4805,7 +4803,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="93"/>
+      <c r="B16" s="102"/>
       <c r="C16" s="19" t="s">
         <v>226</v>
       </c>
@@ -4910,14 +4908,14 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
         <v>42</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D20" s="42" t="s">
         <v>472</v>
@@ -4935,11 +4933,11 @@
         <v>72</v>
       </c>
       <c r="I20" s="44" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="95"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="62" t="s">
         <v>43</v>
       </c>
@@ -4950,7 +4948,7 @@
         <v>335</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>442</v>
@@ -4962,12 +4960,12 @@
         <v>488</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="95"/>
-      <c r="B22" s="91" t="s">
+      <c r="A22" s="94"/>
+      <c r="B22" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -4986,15 +4984,15 @@
         <v>334</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="95"/>
-      <c r="B23" s="92"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="101"/>
       <c r="C23" s="19" t="s">
         <v>109</v>
       </c>
@@ -5018,8 +5016,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="95"/>
-      <c r="B24" s="92"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="101"/>
       <c r="C24" s="19" t="s">
         <v>336</v>
       </c>
@@ -5043,8 +5041,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="95"/>
-      <c r="B25" s="92"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="101"/>
       <c r="C25" s="19" t="s">
         <v>228</v>
       </c>
@@ -5068,8 +5066,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="95"/>
-      <c r="B26" s="92"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="101"/>
       <c r="C26" s="65" t="s">
         <v>227</v>
       </c>
@@ -5093,10 +5091,10 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="95"/>
-      <c r="B27" s="93"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="102"/>
       <c r="C27" s="19" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>284</v>
@@ -5118,7 +5116,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="95"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="62" t="s">
         <v>58</v>
       </c>
@@ -5145,7 +5143,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="95"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="62" t="s">
         <v>13</v>
       </c>
@@ -5172,7 +5170,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="96"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="63" t="s">
         <v>59</v>
       </c>
@@ -5199,7 +5197,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="97" t="s">
+      <c r="A31" s="96" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="61" t="s">
@@ -5215,7 +5213,7 @@
         <v>320</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G31" s="23" t="s">
         <v>316</v>
@@ -5228,7 +5226,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="98"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="62" t="s">
         <v>43</v>
       </c>
@@ -5236,7 +5234,7 @@
         <v>211</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>456</v>
@@ -5251,12 +5249,12 @@
         <v>99</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="98"/>
-      <c r="B33" s="91" t="s">
+      <c r="A33" s="97"/>
+      <c r="B33" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -5282,8 +5280,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="98"/>
-      <c r="B34" s="92"/>
+      <c r="A34" s="97"/>
+      <c r="B34" s="101"/>
       <c r="C34" s="19" t="s">
         <v>100</v>
       </c>
@@ -5297,7 +5295,7 @@
         <v>101</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>102</v>
@@ -5307,8 +5305,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="98"/>
-      <c r="B35" s="92"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="101"/>
       <c r="C35" s="19" t="s">
         <v>103</v>
       </c>
@@ -5332,8 +5330,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="98"/>
-      <c r="B36" s="92"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="101"/>
       <c r="C36" s="19" t="s">
         <v>107</v>
       </c>
@@ -5357,8 +5355,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="98"/>
-      <c r="B37" s="92"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="101"/>
       <c r="C37" s="19" t="s">
         <v>226</v>
       </c>
@@ -5382,7 +5380,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="98"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="62" t="s">
         <v>58</v>
       </c>
@@ -5409,7 +5407,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="98"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="62" t="s">
         <v>13</v>
       </c>
@@ -5436,7 +5434,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="98"/>
+      <c r="A40" s="97"/>
       <c r="B40" s="62" t="s">
         <v>59</v>
       </c>
@@ -5914,8 +5912,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="99"/>
-      <c r="B3" s="100"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="3">
         <v>46188</v>
       </c>
@@ -6054,7 +6052,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D8" s="30" t="s">
         <v>27</v>
@@ -6063,7 +6061,7 @@
         <v>127</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G8" s="30" t="s">
         <v>261</v>
@@ -6113,7 +6111,7 @@
         <v>353</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>352</v>
@@ -6122,10 +6120,10 @@
         <v>462</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>358</v>
@@ -6133,7 +6131,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -6152,7 +6150,7 @@
         <v>129</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>365</v>
@@ -6160,12 +6158,12 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="92"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="31" t="s">
         <v>355</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E12" s="20" t="s">
         <v>361</v>
@@ -6185,7 +6183,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="92"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="31" t="s">
         <v>360</v>
       </c>
@@ -6199,7 +6197,7 @@
         <v>367</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>368</v>
@@ -6210,7 +6208,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="92"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="31" t="s">
         <v>370</v>
       </c>
@@ -6235,7 +6233,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="92"/>
+      <c r="B15" s="101"/>
       <c r="C15" s="31" t="s">
         <v>375</v>
       </c>
@@ -6260,7 +6258,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="93"/>
+      <c r="B16" s="102"/>
       <c r="C16" s="31" t="s">
         <v>137</v>
       </c>
@@ -6271,7 +6269,7 @@
         <v>134</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>378</v>
@@ -6355,7 +6353,7 @@
         <v>380</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H19" s="38" t="s">
         <v>87</v>
@@ -6365,7 +6363,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
@@ -6394,7 +6392,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="95"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -6405,7 +6403,7 @@
         <v>188</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>381</v>
@@ -6421,8 +6419,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="95"/>
-      <c r="B22" s="101" t="s">
+      <c r="A22" s="94"/>
+      <c r="B22" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -6441,15 +6439,15 @@
         <v>388</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="95"/>
-      <c r="B23" s="102"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="31" t="s">
         <v>143</v>
       </c>
@@ -6473,8 +6471,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="95"/>
-      <c r="B24" s="102"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
@@ -6498,8 +6496,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="95"/>
-      <c r="B25" s="102"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="31" t="s">
         <v>393</v>
       </c>
@@ -6523,8 +6521,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="95"/>
-      <c r="B26" s="102"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="92"/>
       <c r="C26" s="31" t="s">
         <v>51</v>
       </c>
@@ -6548,8 +6546,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="95"/>
-      <c r="B27" s="103"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="93"/>
       <c r="C27" s="31" t="s">
         <v>351</v>
       </c>
@@ -6573,7 +6571,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="95"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="17" t="s">
         <v>58</v>
       </c>
@@ -6600,7 +6598,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="95"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -6627,7 +6625,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="96"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="38" t="s">
         <v>59</v>
       </c>
@@ -6654,7 +6652,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="97" t="s">
+      <c r="A31" s="96" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -6683,7 +6681,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="98"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -6691,7 +6689,7 @@
         <v>353</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E32" s="20" t="s">
         <v>352</v>
@@ -6700,18 +6698,18 @@
         <v>462</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="98"/>
-      <c r="B33" s="101" t="s">
+      <c r="A33" s="97"/>
+      <c r="B33" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="31" t="s">
@@ -6730,15 +6728,15 @@
         <v>129</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="98"/>
-      <c r="B34" s="102"/>
+      <c r="A34" s="97"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="31" t="s">
         <v>355</v>
       </c>
@@ -6762,8 +6760,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="98"/>
-      <c r="B35" s="102"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="92"/>
       <c r="C35" s="31" t="s">
         <v>370</v>
       </c>
@@ -6787,8 +6785,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="98"/>
-      <c r="B36" s="102"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="92"/>
       <c r="C36" s="31" t="s">
         <v>375</v>
       </c>
@@ -6812,8 +6810,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="98"/>
-      <c r="B37" s="102"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="31" t="s">
         <v>137</v>
       </c>
@@ -6824,7 +6822,7 @@
         <v>134</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>378</v>
@@ -6837,7 +6835,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="98"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="17" t="s">
         <v>58</v>
       </c>
@@ -6864,7 +6862,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="98"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -6891,7 +6889,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="98"/>
+      <c r="A40" s="97"/>
       <c r="B40" s="17" t="s">
         <v>59</v>
       </c>
@@ -6908,7 +6906,7 @@
         <v>380</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H40" s="38" t="s">
         <v>87</v>
@@ -7358,8 +7356,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="99"/>
-      <c r="B3" s="100"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="84"/>
       <c r="C3" s="3">
         <v>46195</v>
       </c>
@@ -7513,7 +7511,7 @@
         <v>158</v>
       </c>
       <c r="H8" s="68" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I8" s="75" t="s">
         <v>404</v>
@@ -7536,7 +7534,7 @@
         <v>32</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G9" s="23" t="s">
         <v>405</v>
@@ -7545,7 +7543,7 @@
         <v>238</v>
       </c>
       <c r="I9" s="44" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7560,13 +7558,13 @@
         <v>406</v>
       </c>
       <c r="E10" s="64" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>407</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>418</v>
@@ -7577,11 +7575,11 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>204</v>
@@ -7604,7 +7602,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="92"/>
+      <c r="B12" s="101"/>
       <c r="C12" s="19" t="s">
         <v>162</v>
       </c>
@@ -7629,7 +7627,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="92"/>
+      <c r="B13" s="101"/>
       <c r="C13" s="19" t="s">
         <v>411</v>
       </c>
@@ -7654,7 +7652,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="92"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="19" t="s">
         <v>241</v>
       </c>
@@ -7679,7 +7677,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="92"/>
+      <c r="B15" s="101"/>
       <c r="C15" s="19" t="s">
         <v>240</v>
       </c>
@@ -7704,7 +7702,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="93"/>
+      <c r="B16" s="102"/>
       <c r="C16" s="19" t="s">
         <v>476</v>
       </c>
@@ -7809,7 +7807,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
@@ -7838,7 +7836,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="95"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="62" t="s">
         <v>43</v>
       </c>
@@ -7861,12 +7859,12 @@
         <v>422</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="95"/>
-      <c r="B22" s="91" t="s">
+      <c r="A22" s="94"/>
+      <c r="B22" s="100" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -7892,8 +7890,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="95"/>
-      <c r="B23" s="92"/>
+      <c r="A23" s="94"/>
+      <c r="B23" s="101"/>
       <c r="C23" s="19" t="s">
         <v>169</v>
       </c>
@@ -7917,8 +7915,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="95"/>
-      <c r="B24" s="92"/>
+      <c r="A24" s="94"/>
+      <c r="B24" s="101"/>
       <c r="C24" s="19" t="s">
         <v>173</v>
       </c>
@@ -7942,8 +7940,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="95"/>
-      <c r="B25" s="92"/>
+      <c r="A25" s="94"/>
+      <c r="B25" s="101"/>
       <c r="C25" s="19" t="s">
         <v>103</v>
       </c>
@@ -7960,15 +7958,15 @@
         <v>255</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="95"/>
-      <c r="B26" s="92"/>
+      <c r="A26" s="94"/>
+      <c r="B26" s="101"/>
       <c r="C26" s="19" t="s">
         <v>250</v>
       </c>
@@ -7985,15 +7983,15 @@
         <v>175</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="95"/>
-      <c r="B27" s="93"/>
+      <c r="A27" s="94"/>
+      <c r="B27" s="102"/>
       <c r="C27" s="19" t="s">
         <v>432</v>
       </c>
@@ -8017,7 +8015,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="95"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="62" t="s">
         <v>58</v>
       </c>
@@ -8044,7 +8042,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="95"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="62" t="s">
         <v>13</v>
       </c>
@@ -8071,7 +8069,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="96"/>
+      <c r="A30" s="95"/>
       <c r="B30" s="63" t="s">
         <v>59</v>
       </c>
@@ -8098,7 +8096,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="97" t="s">
+      <c r="A31" s="96" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -8114,7 +8112,7 @@
         <v>32</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G31" s="23" t="s">
         <v>405</v>
@@ -8123,11 +8121,11 @@
         <v>238</v>
       </c>
       <c r="I31" s="44" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="98"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -8138,13 +8136,13 @@
         <v>406</v>
       </c>
       <c r="E32" s="64" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F32" s="17" t="s">
         <v>407</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>418</v>
@@ -8154,12 +8152,12 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="98"/>
-      <c r="B33" s="101" t="s">
+      <c r="A33" s="97"/>
+      <c r="B33" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>204</v>
@@ -8181,8 +8179,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="98"/>
-      <c r="B34" s="102"/>
+      <c r="A34" s="97"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="19" t="s">
         <v>162</v>
       </c>
@@ -8206,8 +8204,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="98"/>
-      <c r="B35" s="102"/>
+      <c r="A35" s="97"/>
+      <c r="B35" s="92"/>
       <c r="C35" s="19" t="s">
         <v>241</v>
       </c>
@@ -8231,8 +8229,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="98"/>
-      <c r="B36" s="102"/>
+      <c r="A36" s="97"/>
+      <c r="B36" s="92"/>
       <c r="C36" s="19" t="s">
         <v>240</v>
       </c>
@@ -8256,8 +8254,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="98"/>
-      <c r="B37" s="102"/>
+      <c r="A37" s="97"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="19" t="s">
         <v>476</v>
       </c>
@@ -8281,7 +8279,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="98"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="17" t="s">
         <v>58</v>
       </c>
@@ -8308,7 +8306,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="98"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -8335,7 +8333,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="98"/>
+      <c r="A40" s="97"/>
       <c r="B40" s="17" t="s">
         <v>59</v>
       </c>

--- a/source/Hoyeh Menu Jun 26.xlsx
+++ b/source/Hoyeh Menu Jun 26.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrgroupsg-my.sharepoint.com/personal/om_hoyeh_jrgroup_com_sg/Documents/Desktop/menu-rws hoyeh/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{6B9EBA44-D3D0-4669-8BA1-A8183BB88044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C1C835E-AE1B-4DDD-B632-EEB3552D8CB7}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{6B9EBA44-D3D0-4669-8BA1-A8183BB88044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B3D5C4B-A0E7-408F-9A92-CD6945262550}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{3D15533C-2B3B-4150-90D8-B42A3F2F21C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2579,6 +2580,24 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2588,12 +2607,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2604,18 +2617,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3219,7 +3220,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="97" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -3246,7 +3247,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="92"/>
+      <c r="B12" s="98"/>
       <c r="C12" s="19" t="s">
         <v>270</v>
       </c>
@@ -3271,7 +3272,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="92"/>
+      <c r="B13" s="98"/>
       <c r="C13" s="65" t="s">
         <v>444</v>
       </c>
@@ -3296,7 +3297,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="92"/>
+      <c r="B14" s="98"/>
       <c r="C14" s="19" t="s">
         <v>81</v>
       </c>
@@ -3321,7 +3322,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="92"/>
+      <c r="B15" s="98"/>
       <c r="C15" s="19" t="s">
         <v>51</v>
       </c>
@@ -3346,7 +3347,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="93"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
@@ -3451,7 +3452,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="95" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="32" t="s">
@@ -3480,7 +3481,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="94"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -3507,8 +3508,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="94"/>
-      <c r="B22" s="91" t="s">
+      <c r="A22" s="95"/>
+      <c r="B22" s="97" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -3534,8 +3535,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="94"/>
-      <c r="B23" s="92"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="31" t="s">
         <v>450</v>
       </c>
@@ -3559,8 +3560,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="94"/>
-      <c r="B24" s="92"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="31" t="s">
         <v>77</v>
       </c>
@@ -3584,8 +3585,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="94"/>
-      <c r="B25" s="92"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="19" t="s">
         <v>301</v>
       </c>
@@ -3609,8 +3610,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="94"/>
-      <c r="B26" s="92"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="98"/>
       <c r="C26" s="19" t="s">
         <v>113</v>
       </c>
@@ -3634,8 +3635,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="94"/>
-      <c r="B27" s="93"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="99"/>
       <c r="C27" s="20" t="s">
         <v>83</v>
       </c>
@@ -3659,7 +3660,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="17" t="s">
         <v>58</v>
       </c>
@@ -3686,7 +3687,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="94"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -3713,7 +3714,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="95"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="38" t="s">
         <v>59</v>
       </c>
@@ -3740,7 +3741,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="100" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -3769,7 +3770,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="97"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -3796,8 +3797,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="97"/>
-      <c r="B33" s="91" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="97" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -3823,8 +3824,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="97"/>
-      <c r="B34" s="92"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="19" t="s">
         <v>270</v>
       </c>
@@ -3848,8 +3849,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="97"/>
-      <c r="B35" s="92"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="98"/>
       <c r="C35" s="19" t="s">
         <v>81</v>
       </c>
@@ -3873,8 +3874,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="97"/>
-      <c r="B36" s="92"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="19" t="s">
         <v>51</v>
       </c>
@@ -3898,8 +3899,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="97"/>
-      <c r="B37" s="92"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="19" t="s">
         <v>28</v>
       </c>
@@ -3923,7 +3924,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="97"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="17" t="s">
         <v>58</v>
       </c>
@@ -3950,7 +3951,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="97"/>
+      <c r="A39" s="101"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -4457,8 +4458,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
+      <c r="A3" s="102"/>
+      <c r="B3" s="103"/>
       <c r="C3" s="66">
         <v>46181</v>
       </c>
@@ -4676,7 +4677,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -4703,7 +4704,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="101"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="19" t="s">
         <v>100</v>
       </c>
@@ -4728,7 +4729,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="101"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="19" t="s">
         <v>317</v>
       </c>
@@ -4753,7 +4754,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="101"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="19" t="s">
         <v>103</v>
       </c>
@@ -4778,7 +4779,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="101"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="19" t="s">
         <v>107</v>
       </c>
@@ -4803,7 +4804,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="102"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="19" t="s">
         <v>226</v>
       </c>
@@ -4908,7 +4909,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
@@ -4937,7 +4938,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="94"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="62" t="s">
         <v>43</v>
       </c>
@@ -4964,8 +4965,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="94"/>
-      <c r="B22" s="100" t="s">
+      <c r="A22" s="95"/>
+      <c r="B22" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -4991,8 +4992,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="94"/>
-      <c r="B23" s="101"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="19" t="s">
         <v>109</v>
       </c>
@@ -5016,8 +5017,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="94"/>
-      <c r="B24" s="101"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="19" t="s">
         <v>336</v>
       </c>
@@ -5041,8 +5042,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="94"/>
-      <c r="B25" s="101"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="19" t="s">
         <v>228</v>
       </c>
@@ -5066,8 +5067,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="94"/>
-      <c r="B26" s="101"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="92"/>
       <c r="C26" s="65" t="s">
         <v>227</v>
       </c>
@@ -5091,8 +5092,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="94"/>
-      <c r="B27" s="102"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="93"/>
       <c r="C27" s="19" t="s">
         <v>505</v>
       </c>
@@ -5116,7 +5117,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="62" t="s">
         <v>58</v>
       </c>
@@ -5143,7 +5144,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="94"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="62" t="s">
         <v>13</v>
       </c>
@@ -5170,7 +5171,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="95"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="63" t="s">
         <v>59</v>
       </c>
@@ -5197,7 +5198,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="100" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="61" t="s">
@@ -5226,7 +5227,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="97"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="62" t="s">
         <v>43</v>
       </c>
@@ -5253,8 +5254,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="97"/>
-      <c r="B33" s="100" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -5280,8 +5281,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="97"/>
-      <c r="B34" s="101"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="19" t="s">
         <v>100</v>
       </c>
@@ -5305,8 +5306,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="97"/>
-      <c r="B35" s="101"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="92"/>
       <c r="C35" s="19" t="s">
         <v>103</v>
       </c>
@@ -5330,8 +5331,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="97"/>
-      <c r="B36" s="101"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="92"/>
       <c r="C36" s="19" t="s">
         <v>107</v>
       </c>
@@ -5355,8 +5356,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="97"/>
-      <c r="B37" s="101"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="19" t="s">
         <v>226</v>
       </c>
@@ -5380,7 +5381,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="97"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="62" t="s">
         <v>58</v>
       </c>
@@ -5407,7 +5408,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="97"/>
+      <c r="A39" s="101"/>
       <c r="B39" s="62" t="s">
         <v>13</v>
       </c>
@@ -5434,7 +5435,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="97"/>
+      <c r="A40" s="101"/>
       <c r="B40" s="62" t="s">
         <v>59</v>
       </c>
@@ -6131,7 +6132,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -6158,7 +6159,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="101"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="31" t="s">
         <v>355</v>
       </c>
@@ -6183,7 +6184,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="101"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="31" t="s">
         <v>360</v>
       </c>
@@ -6208,7 +6209,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="101"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="31" t="s">
         <v>370</v>
       </c>
@@ -6233,7 +6234,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="101"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="31" t="s">
         <v>375</v>
       </c>
@@ -6258,7 +6259,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="102"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="31" t="s">
         <v>137</v>
       </c>
@@ -6363,7 +6364,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="23" t="s">
@@ -6392,7 +6393,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="94"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="17" t="s">
         <v>43</v>
       </c>
@@ -6419,8 +6420,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="94"/>
-      <c r="B22" s="91" t="s">
+      <c r="A22" s="95"/>
+      <c r="B22" s="97" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="31" t="s">
@@ -6446,8 +6447,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="94"/>
-      <c r="B23" s="92"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="31" t="s">
         <v>143</v>
       </c>
@@ -6471,8 +6472,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="94"/>
-      <c r="B24" s="92"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
@@ -6496,8 +6497,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="94"/>
-      <c r="B25" s="92"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="31" t="s">
         <v>393</v>
       </c>
@@ -6521,8 +6522,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="94"/>
-      <c r="B26" s="92"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="98"/>
       <c r="C26" s="31" t="s">
         <v>51</v>
       </c>
@@ -6546,8 +6547,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="94"/>
-      <c r="B27" s="93"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="99"/>
       <c r="C27" s="31" t="s">
         <v>351</v>
       </c>
@@ -6571,7 +6572,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="17" t="s">
         <v>58</v>
       </c>
@@ -6598,7 +6599,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="94"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="17" t="s">
         <v>13</v>
       </c>
@@ -6625,7 +6626,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="95"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="38" t="s">
         <v>59</v>
       </c>
@@ -6652,7 +6653,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="100" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -6681,7 +6682,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="97"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -6708,8 +6709,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="97"/>
-      <c r="B33" s="91" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="97" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="31" t="s">
@@ -6735,8 +6736,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="97"/>
-      <c r="B34" s="92"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="31" t="s">
         <v>355</v>
       </c>
@@ -6760,8 +6761,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="97"/>
-      <c r="B35" s="92"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="98"/>
       <c r="C35" s="31" t="s">
         <v>370</v>
       </c>
@@ -6785,8 +6786,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="97"/>
-      <c r="B36" s="92"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="31" t="s">
         <v>375</v>
       </c>
@@ -6810,8 +6811,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="97"/>
-      <c r="B37" s="92"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="31" t="s">
         <v>137</v>
       </c>
@@ -6835,7 +6836,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="97"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="17" t="s">
         <v>58</v>
       </c>
@@ -6862,7 +6863,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="97"/>
+      <c r="A39" s="101"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -6889,7 +6890,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="97"/>
+      <c r="A40" s="101"/>
       <c r="B40" s="17" t="s">
         <v>59</v>
       </c>
@@ -7575,7 +7576,7 @@
     </row>
     <row r="11" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="89"/>
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C11" s="19" t="s">
@@ -7602,7 +7603,7 @@
     </row>
     <row r="12" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="89"/>
-      <c r="B12" s="101"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="19" t="s">
         <v>162</v>
       </c>
@@ -7627,7 +7628,7 @@
     </row>
     <row r="13" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="89"/>
-      <c r="B13" s="101"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="19" t="s">
         <v>411</v>
       </c>
@@ -7652,7 +7653,7 @@
     </row>
     <row r="14" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="89"/>
-      <c r="B14" s="101"/>
+      <c r="B14" s="92"/>
       <c r="C14" s="19" t="s">
         <v>241</v>
       </c>
@@ -7677,7 +7678,7 @@
     </row>
     <row r="15" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="89"/>
-      <c r="B15" s="101"/>
+      <c r="B15" s="92"/>
       <c r="C15" s="19" t="s">
         <v>240</v>
       </c>
@@ -7702,7 +7703,7 @@
     </row>
     <row r="16" spans="1:9" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="89"/>
-      <c r="B16" s="102"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="19" t="s">
         <v>476</v>
       </c>
@@ -7770,7 +7771,7 @@
         <v>223</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>30</v>
+        <v>287</v>
       </c>
       <c r="H18" s="17" t="s">
         <v>168</v>
@@ -7807,7 +7808,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="61" t="s">
@@ -7836,7 +7837,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="94"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="62" t="s">
         <v>43</v>
       </c>
@@ -7863,8 +7864,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="94"/>
-      <c r="B22" s="100" t="s">
+      <c r="A22" s="95"/>
+      <c r="B22" s="91" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -7890,8 +7891,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="94"/>
-      <c r="B23" s="101"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="19" t="s">
         <v>169</v>
       </c>
@@ -7915,8 +7916,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="94"/>
-      <c r="B24" s="101"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="19" t="s">
         <v>173</v>
       </c>
@@ -7940,8 +7941,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="94"/>
-      <c r="B25" s="101"/>
+      <c r="A25" s="95"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="19" t="s">
         <v>103</v>
       </c>
@@ -7965,8 +7966,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="94"/>
-      <c r="B26" s="101"/>
+      <c r="A26" s="95"/>
+      <c r="B26" s="92"/>
       <c r="C26" s="19" t="s">
         <v>250</v>
       </c>
@@ -7990,8 +7991,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="94"/>
-      <c r="B27" s="102"/>
+      <c r="A27" s="95"/>
+      <c r="B27" s="93"/>
       <c r="C27" s="19" t="s">
         <v>432</v>
       </c>
@@ -8015,7 +8016,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="94"/>
+      <c r="A28" s="95"/>
       <c r="B28" s="62" t="s">
         <v>58</v>
       </c>
@@ -8042,7 +8043,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="94"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="62" t="s">
         <v>13</v>
       </c>
@@ -8069,7 +8070,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="95"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="63" t="s">
         <v>59</v>
       </c>
@@ -8096,7 +8097,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="100" t="s">
         <v>16</v>
       </c>
       <c r="B31" s="23" t="s">
@@ -8125,7 +8126,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="97"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="17" t="s">
         <v>43</v>
       </c>
@@ -8152,8 +8153,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="97"/>
-      <c r="B33" s="91" t="s">
+      <c r="A33" s="101"/>
+      <c r="B33" s="97" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="19" t="s">
@@ -8179,8 +8180,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="97"/>
-      <c r="B34" s="92"/>
+      <c r="A34" s="101"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="19" t="s">
         <v>162</v>
       </c>
@@ -8204,8 +8205,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="97"/>
-      <c r="B35" s="92"/>
+      <c r="A35" s="101"/>
+      <c r="B35" s="98"/>
       <c r="C35" s="19" t="s">
         <v>241</v>
       </c>
@@ -8229,8 +8230,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="97"/>
-      <c r="B36" s="92"/>
+      <c r="A36" s="101"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="19" t="s">
         <v>240</v>
       </c>
@@ -8254,8 +8255,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="97"/>
-      <c r="B37" s="92"/>
+      <c r="A37" s="101"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="19" t="s">
         <v>476</v>
       </c>
@@ -8279,7 +8280,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="97"/>
+      <c r="A38" s="101"/>
       <c r="B38" s="17" t="s">
         <v>58</v>
       </c>
@@ -8306,7 +8307,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="97"/>
+      <c r="A39" s="101"/>
       <c r="B39" s="17" t="s">
         <v>13</v>
       </c>
@@ -8323,7 +8324,7 @@
         <v>223</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>30</v>
+        <v>287</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>168</v>
@@ -8333,7 +8334,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="7" customFormat="1" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="97"/>
+      <c r="A40" s="101"/>
       <c r="B40" s="17" t="s">
         <v>59</v>
       </c>
@@ -8750,6 +8751,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2FF85B-F427-4533-929D-854FCE734746}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{f472f14c-d40a-4996-84a9-078c3b8640e0}" enabled="1" method="Standard" siteId="{cd62b7dd-4b48-44bd-90e7-e143a22c8ead}" removed="0"/>
